--- a/anthola_fullstack/backend/exports/payments-latest.xlsx
+++ b/anthola_fullstack/backend/exports/payments-latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Payment ID</t>
   </si>
@@ -46,16 +46,16 @@
     <t>Created at</t>
   </si>
   <si>
-    <t>PAY-1781810274679-583</t>
-  </si>
-  <si>
-    <t>6a3444336b3788c55da886c8</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
+    <t>PAY-1785835205715-744</t>
+  </si>
+  <si>
+    <t>6a71aeaf1b05b477e4470a21</t>
+  </si>
+  <si>
+    <t>ktm-pok</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
   </si>
   <si>
     <t>eSewa</t>
@@ -67,58 +67,13 @@
     <t>123456</t>
   </si>
   <si>
-    <t>/uploads/payment-proofs/BKG-1781810227615-667-1781810274675.png</t>
+    <t>/uploads/payment-proofs/BKG-1785835183317-407-1785835205710.png</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-06-18T19:17:54.680Z</t>
-  </si>
-  <si>
-    <t>PAY-1781807142487-438</t>
-  </si>
-  <si>
-    <t>6a3438047d32f505580ee093</t>
-  </si>
-  <si>
-    <t>ktm-Mnr</t>
-  </si>
-  <si>
-    <t>23456</t>
-  </si>
-  <si>
-    <t>/uploads/payment-proofs/BKG-1781807108374-129-1781807142480.png</t>
-  </si>
-  <si>
-    <t>2026-06-18T18:25:42.488Z</t>
-  </si>
-  <si>
-    <t>PAY-1781805310048-789</t>
-  </si>
-  <si>
-    <t>6a3430be30d5ef08203f9951</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>52542586</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>565633</t>
-  </si>
-  <si>
-    <t>/uploads/payment-proofs/BKG-1781805246854-189-1781805310037.png</t>
-  </si>
-  <si>
-    <t>2026-06-18T17:56:29.198Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T17:55:03.413Z</t>
+    <t>2026-08-04T09:20:05.720Z</t>
   </si>
 </sst>
 </file>
@@ -505,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" style="1" customWidth="1"/>
@@ -570,7 +525,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1">
-        <v>8</v>
+        <v>3000</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -586,76 +541,6 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1">
-        <v>10500</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1">
-        <v>22400</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/anthola_fullstack/backend/exports/payments-latest.xlsx
+++ b/anthola_fullstack/backend/exports/payments-latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Payment ID</t>
   </si>
@@ -46,6 +46,57 @@
     <t>Created at</t>
   </si>
   <si>
+    <t>PAY-1785858454342-704</t>
+  </si>
+  <si>
+    <t>6a72098b2bca8e0c6f57ac18</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>eSewa</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>/uploads/payment-proofs/BKG-1785858443846-236-1785858454328.png</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:59:51.319Z</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:47:34.344Z</t>
+  </si>
+  <si>
+    <t>PAY-1785855894866-910</t>
+  </si>
+  <si>
+    <t>6a71ff8624c6b1410eeef249</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>/uploads/payment-proofs/BKG-1785855878390-596-1785855894847.png</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:06:13.275Z</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:04:54.867Z</t>
+  </si>
+  <si>
     <t>PAY-1785835205715-744</t>
   </si>
   <si>
@@ -55,16 +106,7 @@
     <t>ktm-pok</t>
   </si>
   <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>eSewa</t>
-  </si>
-  <si>
     <t>PENDING</t>
-  </si>
-  <si>
-    <t>123456</t>
   </si>
   <si>
     <t>/uploads/payment-proofs/BKG-1785835183317-407-1785835205710.png</t>
@@ -460,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" style="1" customWidth="1"/>
@@ -525,7 +567,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1">
-        <v>3000</v>
+        <v>3398</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -541,6 +583,76 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1">
+        <v>6796</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
